--- a/data.xlsx
+++ b/data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\BC-Whatsapp\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\MAMOSDEV\BC-Whatsapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74047120-6832-44F7-9F5C-09EF9C85092E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196E5F49-6645-47DE-A325-FC2832F7177C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2840" yWindow="2840" windowWidth="14400" windowHeight="7810" xr2:uid="{700DAD14-C686-4A9B-9611-0D8F62E86130}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{700DAD14-C686-4A9B-9611-0D8F62E86130}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
   <si>
     <t>Nama Lengkap</t>
   </si>
@@ -34,6 +34,15 @@
   </si>
   <si>
     <t>Telepon</t>
+  </si>
+  <si>
+    <t>Mahatma</t>
+  </si>
+  <si>
+    <t>Lulus</t>
+  </si>
+  <si>
+    <t>Rosyid</t>
   </si>
 </sst>
 </file>
@@ -420,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563C3881-1F62-4562-8287-1EA757B381C8}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.08984375" bestFit="1" customWidth="1"/>
@@ -438,6 +447,28 @@
         <v>2</v>
       </c>
     </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3">
+        <v>62895328262362</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="3">
+        <v>6287882835355</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\MAMOSDEV\BC-Whatsapp\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196E5F49-6645-47DE-A325-FC2832F7177C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5786C5-C999-48D6-ACB5-87DA38C35A82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{700DAD14-C686-4A9B-9611-0D8F62E86130}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Nama Lengkap</t>
   </si>
@@ -34,15 +34,6 @@
   </si>
   <si>
     <t>Telepon</t>
-  </si>
-  <si>
-    <t>Mahatma</t>
-  </si>
-  <si>
-    <t>Lulus</t>
-  </si>
-  <si>
-    <t>Rosyid</t>
   </si>
 </sst>
 </file>
@@ -429,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{563C3881-1F62-4562-8287-1EA757B381C8}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="36.08984375" bestFit="1" customWidth="1"/>
@@ -447,28 +438,6 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3">
-        <v>62895328262362</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>6287882835355</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
